--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G560"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15516,6 +15516,141 @@
         <v>395.13</v>
       </c>
       <c r="G560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="C561" t="n">
+        <v>416.26</v>
+      </c>
+      <c r="D561" t="n">
+        <v>414.87</v>
+      </c>
+      <c r="E561" t="n">
+        <v>403.46</v>
+      </c>
+      <c r="F561" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="C562" t="n">
+        <v>412.86</v>
+      </c>
+      <c r="D562" t="n">
+        <v>414.93</v>
+      </c>
+      <c r="E562" t="n">
+        <v>402.45</v>
+      </c>
+      <c r="F562" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="C563" t="n">
+        <v>410.34</v>
+      </c>
+      <c r="D563" t="n">
+        <v>413.99</v>
+      </c>
+      <c r="E563" t="n">
+        <v>401.68</v>
+      </c>
+      <c r="F563" t="n">
+        <v>394.41</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="C564" t="n">
+        <v>410.41</v>
+      </c>
+      <c r="D564" t="n">
+        <v>414.06</v>
+      </c>
+      <c r="E564" t="n">
+        <v>402.58</v>
+      </c>
+      <c r="F564" t="n">
+        <v>395.36</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="C565" t="n">
+        <v>409.78</v>
+      </c>
+      <c r="D565" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="E565" t="n">
+        <v>402.91</v>
+      </c>
+      <c r="F565" t="n">
+        <v>395.28</v>
+      </c>
+      <c r="G565" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15532,7 +15667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21945,6 +22080,56 @@
       </c>
       <c r="B641" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -22113,28 +22298,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9194423588088533</v>
+        <v>0.9477650040968075</v>
       </c>
       <c r="J2" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1224102221371302</v>
+        <v>0.1306288513572296</v>
       </c>
       <c r="M2" t="n">
-        <v>14.90384674975582</v>
+        <v>14.9297985885271</v>
       </c>
       <c r="N2" t="n">
-        <v>355.1530010252351</v>
+        <v>354.4699365740321</v>
       </c>
       <c r="O2" t="n">
-        <v>18.84550346966711</v>
+        <v>18.8273720039211</v>
       </c>
       <c r="P2" t="n">
-        <v>320.9944194629273</v>
+        <v>320.7039775544738</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22195,28 +22380,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.968385095672122</v>
+        <v>2.03097200234876</v>
       </c>
       <c r="J3" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2035702665668565</v>
+        <v>0.2152394759833549</v>
       </c>
       <c r="M3" t="n">
-        <v>23.83291617859673</v>
+        <v>23.84257032028061</v>
       </c>
       <c r="N3" t="n">
-        <v>898.8538008476205</v>
+        <v>902.057946701093</v>
       </c>
       <c r="O3" t="n">
-        <v>29.98089059463745</v>
+        <v>30.03427952691879</v>
       </c>
       <c r="P3" t="n">
-        <v>322.9742349563414</v>
+        <v>322.3328180631929</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22277,28 +22462,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.215084513188007</v>
+        <v>1.260144743958591</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2847489685932449</v>
+        <v>0.2986365181983064</v>
       </c>
       <c r="M4" t="n">
-        <v>11.09541840442238</v>
+        <v>11.19234146921608</v>
       </c>
       <c r="N4" t="n">
-        <v>216.978436027151</v>
+        <v>220.7903502382991</v>
       </c>
       <c r="O4" t="n">
-        <v>14.73018791554103</v>
+        <v>14.85901578969143</v>
       </c>
       <c r="P4" t="n">
-        <v>355.7869213570159</v>
+        <v>355.3244889018689</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22355,28 +22540,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8877076920876978</v>
+        <v>0.91299821271019</v>
       </c>
       <c r="J5" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2992202731864994</v>
+        <v>0.3120202714016774</v>
       </c>
       <c r="M5" t="n">
-        <v>8.064146839229128</v>
+        <v>8.116620754174303</v>
       </c>
       <c r="N5" t="n">
-        <v>106.8495107254015</v>
+        <v>107.6801228613065</v>
       </c>
       <c r="O5" t="n">
-        <v>10.33680369966469</v>
+        <v>10.37690333680075</v>
       </c>
       <c r="P5" t="n">
-        <v>364.3122241306687</v>
+        <v>364.0505661866847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22433,28 +22618,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8343765614284482</v>
+        <v>0.8524773170621396</v>
       </c>
       <c r="J6" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="K6" t="n">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1838217621743334</v>
+        <v>0.1927578956969633</v>
       </c>
       <c r="M6" t="n">
-        <v>10.60653291854496</v>
+        <v>10.59956128759132</v>
       </c>
       <c r="N6" t="n">
-        <v>180.8504307228573</v>
+        <v>180.1757261337638</v>
       </c>
       <c r="O6" t="n">
-        <v>13.44806419983401</v>
+        <v>13.4229551937628</v>
       </c>
       <c r="P6" t="n">
-        <v>362.5056470812094</v>
+        <v>362.3198913655377</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22492,7 +22677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G560"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43135,6 +43320,191 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-36.836456474870616,174.42730591676036</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-36.83592711654424,174.42651698728287</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-36.83524778469123,174.42622188609155</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-36.834536530137626,174.42603188347107</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-36.833840431982736,174.42579195213497</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-36.83642898483522,174.4273964377873</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-36.83591628638433,174.4265526501279</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-36.83524797581056,174.42622125675214</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-36.834533312970436,174.42604247725743</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-36.83383495326401,174.42580999288637</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-36.83642898483522,174.4273964377873</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-36.835908259317854,174.4265790825828</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-36.835244981607474,174.42623111640256</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-36.834530860277994,174.4260505537078</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-36.833832787258196,174.42581712527576</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-36.83642124429162,174.42742192631474</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-36.83590848229201,174.42657834834802</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-36.835245204580076,174.42623038217332</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-36.83453372706131,174.42604111370082</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-36.83383581329561,174.42580716090816</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-36.83641079614193,174.42745633057382</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-36.835906475524524,174.4265849564609</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-36.83524517272686,174.4262304870632</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-36.834534778214994,174.42603765236473</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-36.833835558471435,174.42580800001284</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G565"/>
+  <dimension ref="A1:G566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15653,6 +15653,33 @@
       <c r="G565" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="C566" t="n">
+        <v>409.47</v>
+      </c>
+      <c r="D566" t="n">
+        <v>413.27</v>
+      </c>
+      <c r="E566" t="n">
+        <v>400.26</v>
+      </c>
+      <c r="F566" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15667,7 +15694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B646"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22130,6 +22157,16 @@
       </c>
       <c r="B646" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -22298,28 +22335,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9477650040968075</v>
+        <v>0.9491997968686737</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K2" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1306288513572296</v>
+        <v>0.1314310956601272</v>
       </c>
       <c r="M2" t="n">
-        <v>14.9297985885271</v>
+        <v>14.91127051370687</v>
       </c>
       <c r="N2" t="n">
-        <v>354.4699365740321</v>
+        <v>353.8700752003558</v>
       </c>
       <c r="O2" t="n">
-        <v>18.8273720039211</v>
+        <v>18.81143469277013</v>
       </c>
       <c r="P2" t="n">
-        <v>320.7039775544738</v>
+        <v>320.6892116075994</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22380,28 +22417,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>2.03097200234876</v>
+        <v>2.042220663443564</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2152394759833549</v>
+        <v>0.2174525967270581</v>
       </c>
       <c r="M3" t="n">
-        <v>23.84257032028061</v>
+        <v>23.84144596797563</v>
       </c>
       <c r="N3" t="n">
-        <v>902.057946701093</v>
+        <v>902.2869798535066</v>
       </c>
       <c r="O3" t="n">
-        <v>30.03427952691879</v>
+        <v>30.0380921473636</v>
       </c>
       <c r="P3" t="n">
-        <v>322.3328180631929</v>
+        <v>322.2171396252016</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22462,28 +22499,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.260144743958591</v>
+        <v>1.268478306181264</v>
       </c>
       <c r="J4" t="n">
+        <v>565</v>
+      </c>
+      <c r="K4" t="n">
         <v>564</v>
       </c>
-      <c r="K4" t="n">
-        <v>563</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2986365181983064</v>
+        <v>0.3013152574405439</v>
       </c>
       <c r="M4" t="n">
-        <v>11.19234146921608</v>
+        <v>11.21001514234984</v>
       </c>
       <c r="N4" t="n">
-        <v>220.7903502382991</v>
+        <v>221.4002627950551</v>
       </c>
       <c r="O4" t="n">
-        <v>14.85901578969143</v>
+        <v>14.87952495192824</v>
       </c>
       <c r="P4" t="n">
-        <v>355.3244889018689</v>
+        <v>355.2386832934378</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22540,28 +22577,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.91299821271019</v>
+        <v>0.9170553542618264</v>
       </c>
       <c r="J5" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K5" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3120202714016774</v>
+        <v>0.3143480139401977</v>
       </c>
       <c r="M5" t="n">
-        <v>8.116620754174303</v>
+        <v>8.1221355784783</v>
       </c>
       <c r="N5" t="n">
-        <v>107.6801228613065</v>
+        <v>107.7222940970877</v>
       </c>
       <c r="O5" t="n">
-        <v>10.37690333680075</v>
+        <v>10.37893511382973</v>
       </c>
       <c r="P5" t="n">
-        <v>364.0505661866847</v>
+        <v>364.00845372228</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22618,28 +22655,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8524773170621396</v>
+        <v>0.8550178137879085</v>
       </c>
       <c r="J6" t="n">
+        <v>565</v>
+      </c>
+      <c r="K6" t="n">
         <v>564</v>
       </c>
-      <c r="K6" t="n">
-        <v>563</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1927578956969633</v>
+        <v>0.1942468608500643</v>
       </c>
       <c r="M6" t="n">
-        <v>10.59956128759132</v>
+        <v>10.59290513728473</v>
       </c>
       <c r="N6" t="n">
-        <v>180.1757261337638</v>
+        <v>179.9493285974169</v>
       </c>
       <c r="O6" t="n">
-        <v>13.4229551937628</v>
+        <v>13.41451932040119</v>
       </c>
       <c r="P6" t="n">
-        <v>362.3198913655377</v>
+        <v>362.2937334199381</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22677,7 +22714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G565"/>
+  <dimension ref="A1:G566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43505,6 +43542,43 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-36.83639241629391,174.42751685267686</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-36.835905488067375,174.42658820807188</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-36.8352426881748,174.4262386684747</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-36.83452633712948,174.42606544793955</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-36.83382721297657,174.42583548068768</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G566"/>
+  <dimension ref="A1:G567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15678,6 +15678,33 @@
         <v>392.66</v>
       </c>
       <c r="G566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="C567" t="n">
+        <v>406.19</v>
+      </c>
+      <c r="D567" t="n">
+        <v>412.42</v>
+      </c>
+      <c r="E567" t="n">
+        <v>398.83</v>
+      </c>
+      <c r="F567" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="G567" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15694,7 +15721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22167,6 +22194,16 @@
       </c>
       <c r="B647" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -22335,28 +22372,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9491997968686737</v>
+        <v>0.9466305503333996</v>
       </c>
       <c r="J2" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K2" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1314310956601272</v>
+        <v>0.1312536622898285</v>
       </c>
       <c r="M2" t="n">
-        <v>14.91127051370687</v>
+        <v>14.89652835952608</v>
       </c>
       <c r="N2" t="n">
-        <v>353.8700752003558</v>
+        <v>353.3375655503057</v>
       </c>
       <c r="O2" t="n">
-        <v>18.81143469277013</v>
+        <v>18.79727548210925</v>
       </c>
       <c r="P2" t="n">
-        <v>320.6892116075994</v>
+        <v>320.715749665522</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22417,28 +22454,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>2.042220663443564</v>
+        <v>2.052209043353932</v>
       </c>
       <c r="J3" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2174525967270581</v>
+        <v>0.2195427618000407</v>
       </c>
       <c r="M3" t="n">
-        <v>23.84144596797563</v>
+        <v>23.83529280902304</v>
       </c>
       <c r="N3" t="n">
-        <v>902.2869798535066</v>
+        <v>902.1170429029352</v>
       </c>
       <c r="O3" t="n">
-        <v>30.0380921473636</v>
+        <v>30.03526332334936</v>
       </c>
       <c r="P3" t="n">
-        <v>322.2171396252016</v>
+        <v>322.1140339290866</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22499,28 +22536,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.268478306181264</v>
+        <v>1.276437437382896</v>
       </c>
       <c r="J4" t="n">
+        <v>566</v>
+      </c>
+      <c r="K4" t="n">
         <v>565</v>
       </c>
-      <c r="K4" t="n">
-        <v>564</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.3013152574405439</v>
+        <v>0.3039623010369472</v>
       </c>
       <c r="M4" t="n">
-        <v>11.21001514234984</v>
+        <v>11.22567277273439</v>
       </c>
       <c r="N4" t="n">
-        <v>221.4002627950551</v>
+        <v>221.9173599941342</v>
       </c>
       <c r="O4" t="n">
-        <v>14.87952495192824</v>
+        <v>14.89689095060221</v>
       </c>
       <c r="P4" t="n">
-        <v>355.2386832934378</v>
+        <v>355.1564330228999</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22577,28 +22614,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9170553542618264</v>
+        <v>0.9205597908886143</v>
       </c>
       <c r="J5" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K5" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3143480139401977</v>
+        <v>0.3165445618518441</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1221355784783</v>
+        <v>8.124787532801287</v>
       </c>
       <c r="N5" t="n">
-        <v>107.7222940970877</v>
+        <v>107.7045187789013</v>
       </c>
       <c r="O5" t="n">
-        <v>10.37893511382973</v>
+        <v>10.37807876145201</v>
       </c>
       <c r="P5" t="n">
-        <v>364.00845372228</v>
+        <v>363.9719463322068</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22655,28 +22692,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8550178137879085</v>
+        <v>0.8571415532672234</v>
       </c>
       <c r="J6" t="n">
+        <v>566</v>
+      </c>
+      <c r="K6" t="n">
         <v>565</v>
       </c>
-      <c r="K6" t="n">
-        <v>564</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1942468608500643</v>
+        <v>0.1956181726122543</v>
       </c>
       <c r="M6" t="n">
-        <v>10.59290513728473</v>
+        <v>10.58420820843781</v>
       </c>
       <c r="N6" t="n">
-        <v>179.9493285974169</v>
+        <v>179.695550565424</v>
       </c>
       <c r="O6" t="n">
-        <v>13.41451932040119</v>
+        <v>13.40505690272981</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2937334199381</v>
+        <v>362.271786533739</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22714,7 +22751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G566"/>
+  <dimension ref="A1:G567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43579,6 +43616,43 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-36.83635632544712,174.4276356940852</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-36.83589504012836,174.42662261220846</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-36.8352399806495,174.42624758411486</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-36.834521782125975,174.42608044705844</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-36.833823772847104,174.42584680859764</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
